--- a/artfynd/A 53611-2023 artfynd.xlsx
+++ b/artfynd/A 53611-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127438106</v>
       </c>
       <c r="B2" t="n">
-        <v>97118</v>
+        <v>97122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53611-2023 artfynd.xlsx
+++ b/artfynd/A 53611-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127438106</v>
       </c>
       <c r="B2" t="n">
-        <v>97122</v>
+        <v>97124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53611-2023 artfynd.xlsx
+++ b/artfynd/A 53611-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127438106</v>
       </c>
       <c r="B2" t="n">
-        <v>97124</v>
+        <v>97130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53611-2023 artfynd.xlsx
+++ b/artfynd/A 53611-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127438106</v>
       </c>
       <c r="B2" t="n">
-        <v>97130</v>
+        <v>97133</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53611-2023 artfynd.xlsx
+++ b/artfynd/A 53611-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127438106</v>
       </c>
       <c r="B2" t="n">
-        <v>97133</v>
+        <v>97141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53611-2023 artfynd.xlsx
+++ b/artfynd/A 53611-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127438106</v>
       </c>
       <c r="B2" t="n">
-        <v>97141</v>
+        <v>97142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53611-2023 artfynd.xlsx
+++ b/artfynd/A 53611-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127438106</v>
       </c>
       <c r="B2" t="n">
-        <v>97142</v>
+        <v>97143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53611-2023 artfynd.xlsx
+++ b/artfynd/A 53611-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127438106</v>
       </c>
       <c r="B2" t="n">
-        <v>97143</v>
+        <v>97144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53611-2023 artfynd.xlsx
+++ b/artfynd/A 53611-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127438106</v>
       </c>
       <c r="B2" t="n">
-        <v>97144</v>
+        <v>97780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,6 +787,112 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>108701197</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57602</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100063</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Smålom</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Gavia stellata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hynningen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>349409</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6587538</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sillerud</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-04-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-04-27</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
